--- a/secondary_genes/lung_genes_secondary_results.xlsx
+++ b/secondary_genes/lung_genes_secondary_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/secondary genes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/secondary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{204B8E08-A472-9D44-A63C-D8246BBEE4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBE58CE-9219-AA49-BEAD-9DA43DCF32FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10240" yWindow="0" windowWidth="18560" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10240" yWindow="500" windowWidth="18560" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/secondary_genes/lung_genes_secondary_results.xlsx
+++ b/secondary_genes/lung_genes_secondary_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/secondary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBE58CE-9219-AA49-BEAD-9DA43DCF32FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB549C1-2FBA-0F45-9228-2CAE9DF9C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10240" yWindow="500" windowWidth="18560" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37900" yWindow="500" windowWidth="28240" windowHeight="24440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/secondary_genes/lung_genes_secondary_results.xlsx
+++ b/secondary_genes/lung_genes_secondary_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anqiwang/Documents/GitHub/Ozone-and-Lung-Functions/secondary_genes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB549C1-2FBA-0F45-9228-2CAE9DF9C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC8FF60-699F-8B40-8551-9D6FF8BB05DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37900" yWindow="500" windowWidth="28240" windowHeight="24440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1420" yWindow="2560" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
